--- a/artfynd/A 24131-2025 artfynd.xlsx
+++ b/artfynd/A 24131-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -989,6 +989,354 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126317971</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bötå böj, Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>442667</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6733482</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126319566</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bötå böj, Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>442470</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6733787</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126318186</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bötå böj, Bötå böj, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>442671</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6733554</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24131-2025 artfynd.xlsx
+++ b/artfynd/A 24131-2025 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>126317971</v>
       </c>
       <c r="B5" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>126319566</v>
       </c>
       <c r="B6" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>126318186</v>
       </c>
       <c r="B7" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24131-2025 artfynd.xlsx
+++ b/artfynd/A 24131-2025 artfynd.xlsx
@@ -1110,7 +1110,7 @@
         <v>126319566</v>
       </c>
       <c r="B6" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24131-2025 artfynd.xlsx
+++ b/artfynd/A 24131-2025 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>126317971</v>
       </c>
       <c r="B5" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>126319566</v>
       </c>
       <c r="B6" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>126318186</v>
       </c>
       <c r="B7" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24131-2025 artfynd.xlsx
+++ b/artfynd/A 24131-2025 artfynd.xlsx
@@ -1981,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126532356</v>
+        <v>126534688</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,37 +1992,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442672</v>
+        <v>442816</v>
       </c>
       <c r="R14" t="n">
-        <v>6733497</v>
+        <v>6733589</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,12 +2076,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2302,45 +2302,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126534019</v>
+        <v>126535521</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442849</v>
+        <v>442661</v>
       </c>
       <c r="R17" t="n">
-        <v>6733592</v>
+        <v>6733562</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2377,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2382,7 +2387,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,7 +2414,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126533517</v>
+        <v>126534019</v>
       </c>
       <c r="B18" t="n">
         <v>78980</v>
@@ -2440,14 +2445,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442732</v>
+        <v>442849</v>
       </c>
       <c r="R18" t="n">
-        <v>6733607</v>
+        <v>6733592</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2484,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2489,7 +2494,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,50 +2521,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126535521</v>
+        <v>126533517</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442661</v>
+        <v>442732</v>
       </c>
       <c r="R19" t="n">
-        <v>6733562</v>
+        <v>6733607</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126534688</v>
+        <v>126532356</v>
       </c>
       <c r="B20" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,37 +2639,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442816</v>
+        <v>442672</v>
       </c>
       <c r="R20" t="n">
-        <v>6733589</v>
+        <v>6733497</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,22 +2723,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126533458</v>
+        <v>126545006</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,37 +2746,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442754</v>
+        <v>442689</v>
       </c>
       <c r="R21" t="n">
-        <v>6733597</v>
+        <v>6733596</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2803,49 +2806,40 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126534242</v>
+        <v>126532432</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2853,37 +2847,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442855</v>
+        <v>442670</v>
       </c>
       <c r="R22" t="n">
-        <v>6733530</v>
+        <v>6733482</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2912,7 +2906,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2922,7 +2916,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,22 +2931,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126532432</v>
+        <v>126537728</v>
       </c>
       <c r="B23" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2960,37 +2954,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>442670</v>
+        <v>442529</v>
       </c>
       <c r="R23" t="n">
-        <v>6733482</v>
+        <v>6733634</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3019,7 +3013,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3029,7 +3023,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,19 +3038,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126534869</v>
+        <v>126533458</v>
       </c>
       <c r="B24" t="n">
         <v>78980</v>
@@ -3091,10 +3085,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>442797</v>
+        <v>442754</v>
       </c>
       <c r="R24" t="n">
-        <v>6733657</v>
+        <v>6733597</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3126,7 +3120,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3136,7 +3130,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3163,7 +3157,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126537728</v>
+        <v>126534242</v>
       </c>
       <c r="B25" t="n">
         <v>78980</v>
@@ -3194,14 +3188,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442529</v>
+        <v>442855</v>
       </c>
       <c r="R25" t="n">
-        <v>6733634</v>
+        <v>6733530</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3233,7 +3227,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3243,7 +3237,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3270,10 +3264,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126545006</v>
+        <v>126534869</v>
       </c>
       <c r="B26" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3281,40 +3275,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442689</v>
+        <v>442797</v>
       </c>
       <c r="R26" t="n">
-        <v>6733596</v>
+        <v>6733657</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3341,62 +3332,71 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126536898</v>
+        <v>126536090</v>
       </c>
       <c r="B27" t="n">
-        <v>98395</v>
+        <v>78980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442534</v>
+        <v>442588</v>
       </c>
       <c r="R27" t="n">
-        <v>6733765</v>
+        <v>6733620</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3478,7 +3478,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126536235</v>
+        <v>126534255</v>
       </c>
       <c r="B28" t="n">
         <v>78980</v>
@@ -3509,17 +3509,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>442562</v>
+        <v>442816</v>
       </c>
       <c r="R28" t="n">
-        <v>6733675</v>
+        <v>6733589</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3573,22 +3573,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126545082</v>
+        <v>126535579</v>
       </c>
       <c r="B29" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3596,40 +3596,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>442504</v>
+        <v>442816</v>
       </c>
       <c r="R29" t="n">
-        <v>6733693</v>
+        <v>6733589</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3656,78 +3653,92 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126536090</v>
+        <v>126536329</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442588</v>
+        <v>442595</v>
       </c>
       <c r="R30" t="n">
-        <v>6733620</v>
+        <v>6733618</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3756,7 +3767,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3766,7 +3777,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Balning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3781,60 +3797,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126534255</v>
+        <v>126536898</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>98395</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442816</v>
+        <v>442534</v>
       </c>
       <c r="R31" t="n">
-        <v>6733589</v>
+        <v>6733765</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3863,7 +3879,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3873,7 +3889,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3888,22 +3904,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126535579</v>
+        <v>126536235</v>
       </c>
       <c r="B32" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3911,37 +3927,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>442816</v>
+        <v>442562</v>
       </c>
       <c r="R32" t="n">
-        <v>6733589</v>
+        <v>6733675</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3970,7 +3986,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3980,7 +3996,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3995,65 +4011,63 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126536329</v>
+        <v>126545082</v>
       </c>
       <c r="B33" t="n">
-        <v>56849</v>
+        <v>79598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>442595</v>
+        <v>442504</v>
       </c>
       <c r="R33" t="n">
-        <v>6733618</v>
+        <v>6733693</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4080,44 +4094,30 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Balning</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -5878,57 +5878,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126536612</v>
+        <v>126532174</v>
       </c>
       <c r="B50" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442595</v>
+        <v>442587</v>
       </c>
       <c r="R50" t="n">
-        <v>6733618</v>
+        <v>6733482</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5957,7 +5948,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5967,7 +5958,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5982,22 +5973,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126533900</v>
+        <v>126534774</v>
       </c>
       <c r="B51" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6005,21 +5996,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6029,10 +6020,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442790</v>
+        <v>442828</v>
       </c>
       <c r="R51" t="n">
-        <v>6733600</v>
+        <v>6733596</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6064,7 +6055,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6074,7 +6065,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6101,7 +6092,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126532174</v>
+        <v>126534694</v>
       </c>
       <c r="B52" t="n">
         <v>78980</v>
@@ -6132,14 +6123,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442587</v>
+        <v>442844</v>
       </c>
       <c r="R52" t="n">
-        <v>6733482</v>
+        <v>6733536</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6171,7 +6162,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6181,7 +6172,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6208,48 +6199,57 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126534774</v>
+        <v>126536612</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442828</v>
+        <v>442595</v>
       </c>
       <c r="R53" t="n">
-        <v>6733596</v>
+        <v>6733618</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6303,22 +6303,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126534694</v>
+        <v>126533900</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6326,21 +6326,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6350,10 +6350,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442844</v>
+        <v>442790</v>
       </c>
       <c r="R54" t="n">
-        <v>6733536</v>
+        <v>6733600</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6422,7 +6422,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126532998</v>
+        <v>126533506</v>
       </c>
       <c r="B55" t="n">
         <v>78980</v>
@@ -6453,14 +6453,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>442725</v>
+        <v>442734</v>
       </c>
       <c r="R55" t="n">
-        <v>6733534</v>
+        <v>6733610</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6529,7 +6529,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126534926</v>
+        <v>126533495</v>
       </c>
       <c r="B56" t="n">
         <v>78980</v>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442793</v>
+        <v>442742</v>
       </c>
       <c r="R56" t="n">
-        <v>6733682</v>
+        <v>6733609</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6636,45 +6636,59 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126533506</v>
+        <v>126534189</v>
       </c>
       <c r="B57" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442734</v>
+        <v>442855</v>
       </c>
       <c r="R57" t="n">
-        <v>6733610</v>
+        <v>6733559</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6706,7 +6720,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6716,7 +6730,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Bladrosetter över ca 1kv/m. 30+</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6743,10 +6762,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126533495</v>
+        <v>126533259</v>
       </c>
       <c r="B58" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6754,21 +6773,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6778,10 +6797,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442742</v>
+        <v>442752</v>
       </c>
       <c r="R58" t="n">
-        <v>6733609</v>
+        <v>6733552</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6813,7 +6832,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6823,7 +6842,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6850,62 +6869,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126534189</v>
+        <v>126536931</v>
       </c>
       <c r="B59" t="n">
-        <v>98361</v>
+        <v>80043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442855</v>
+        <v>442595</v>
       </c>
       <c r="R59" t="n">
-        <v>6733559</v>
+        <v>6733618</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6934,7 +6939,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6944,12 +6949,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Bladrosetter över ca 1kv/m. 30+</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6964,22 +6964,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126533259</v>
+        <v>126532998</v>
       </c>
       <c r="B60" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6987,34 +6987,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442752</v>
+        <v>442725</v>
       </c>
       <c r="R60" t="n">
-        <v>6733552</v>
+        <v>6733534</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7083,48 +7083,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126536931</v>
+        <v>126534926</v>
       </c>
       <c r="B61" t="n">
-        <v>80043</v>
+        <v>78980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442595</v>
+        <v>442793</v>
       </c>
       <c r="R61" t="n">
-        <v>6733618</v>
+        <v>6733682</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7178,12 +7178,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8935,59 +8935,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126536344</v>
+        <v>126533153</v>
       </c>
       <c r="B78" t="n">
-        <v>98361</v>
+        <v>56849</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>442554</v>
+        <v>442518</v>
       </c>
       <c r="R78" t="n">
-        <v>6733705</v>
+        <v>6733634</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9019,7 +9005,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9029,7 +9015,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Spillning, äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9044,19 +9035,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126536383</v>
+        <v>126536344</v>
       </c>
       <c r="B79" t="n">
         <v>98361</v>
@@ -9086,7 +9077,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9105,10 +9096,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>442548</v>
+        <v>442554</v>
       </c>
       <c r="R79" t="n">
-        <v>6733706</v>
+        <v>6733705</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9140,7 +9131,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9150,7 +9141,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9177,45 +9168,59 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126533153</v>
+        <v>126536383</v>
       </c>
       <c r="B80" t="n">
-        <v>56849</v>
+        <v>98361</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>442518</v>
+        <v>442548</v>
       </c>
       <c r="R80" t="n">
-        <v>6733634</v>
+        <v>6733706</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9247,7 +9252,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9257,12 +9262,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Spillning, äldre</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9277,12 +9277,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9610,10 +9610,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126532233</v>
+        <v>126544960</v>
       </c>
       <c r="B84" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9621,37 +9621,40 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>442578</v>
+        <v>442834</v>
       </c>
       <c r="R84" t="n">
-        <v>6733497</v>
+        <v>6733542</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9678,46 +9681,37 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126537460</v>
+        <v>126532233</v>
       </c>
       <c r="B85" t="n">
         <v>78980</v>
@@ -9752,10 +9746,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>442496</v>
+        <v>442578</v>
       </c>
       <c r="R85" t="n">
-        <v>6733706</v>
+        <v>6733497</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9787,7 +9781,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9797,7 +9791,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9824,10 +9818,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126544960</v>
+        <v>126537460</v>
       </c>
       <c r="B86" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9835,40 +9829,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>442834</v>
+        <v>442496</v>
       </c>
       <c r="R86" t="n">
-        <v>6733542</v>
+        <v>6733706</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9895,30 +9886,39 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10358,10 +10358,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126545058</v>
+        <v>126545041</v>
       </c>
       <c r="B91" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10369,21 +10369,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>442626</v>
+        <v>442624</v>
       </c>
       <c r="R91" t="n">
-        <v>6733676</v>
+        <v>6733705</v>
       </c>
       <c r="S91" t="n">
         <v>50</v>
@@ -10459,10 +10459,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126545041</v>
+        <v>126544939</v>
       </c>
       <c r="B92" t="n">
-        <v>79598</v>
+        <v>91245</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10470,21 +10470,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10497,10 +10497,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>442624</v>
+        <v>442804</v>
       </c>
       <c r="R92" t="n">
-        <v>6733705</v>
+        <v>6733651</v>
       </c>
       <c r="S92" t="n">
         <v>50</v>
@@ -10560,10 +10560,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126545073</v>
+        <v>126533418</v>
       </c>
       <c r="B93" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10571,40 +10571,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>442502</v>
+        <v>442749</v>
       </c>
       <c r="R93" t="n">
-        <v>6733702</v>
+        <v>6733551</v>
       </c>
       <c r="S93" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10631,40 +10628,49 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126544939</v>
+        <v>126533664</v>
       </c>
       <c r="B94" t="n">
-        <v>91245</v>
+        <v>78739</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10672,40 +10678,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>442804</v>
+        <v>442805</v>
       </c>
       <c r="R94" t="n">
-        <v>6733651</v>
+        <v>6733576</v>
       </c>
       <c r="S94" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10732,40 +10735,49 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126533418</v>
+        <v>126545058</v>
       </c>
       <c r="B95" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10773,37 +10785,40 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>442749</v>
+        <v>442626</v>
       </c>
       <c r="R95" t="n">
-        <v>6733551</v>
+        <v>6733676</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10830,46 +10845,37 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126533664</v>
+        <v>126545073</v>
       </c>
       <c r="B96" t="n">
         <v>78739</v>
@@ -10898,19 +10904,22 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>442805</v>
+        <v>442502</v>
       </c>
       <c r="R96" t="n">
-        <v>6733576</v>
+        <v>6733702</v>
       </c>
       <c r="S96" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10937,39 +10946,30 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>

--- a/artfynd/A 24131-2025 artfynd.xlsx
+++ b/artfynd/A 24131-2025 artfynd.xlsx
@@ -1981,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126534688</v>
+        <v>126532356</v>
       </c>
       <c r="B14" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,37 +1992,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442816</v>
+        <v>442672</v>
       </c>
       <c r="R14" t="n">
-        <v>6733589</v>
+        <v>6733497</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,12 +2076,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2302,50 +2302,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126535521</v>
+        <v>126534019</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442661</v>
+        <v>442849</v>
       </c>
       <c r="R17" t="n">
-        <v>6733562</v>
+        <v>6733592</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,7 +2372,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2387,7 +2382,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,7 +2409,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126534019</v>
+        <v>126533517</v>
       </c>
       <c r="B18" t="n">
         <v>78980</v>
@@ -2445,14 +2440,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442849</v>
+        <v>442732</v>
       </c>
       <c r="R18" t="n">
-        <v>6733592</v>
+        <v>6733607</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,7 +2479,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2494,7 +2489,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2521,45 +2516,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126533517</v>
+        <v>126535521</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442732</v>
+        <v>442661</v>
       </c>
       <c r="R19" t="n">
-        <v>6733607</v>
+        <v>6733562</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126532356</v>
+        <v>126534688</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,37 +2639,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442672</v>
+        <v>442816</v>
       </c>
       <c r="R20" t="n">
-        <v>6733497</v>
+        <v>6733589</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,12 +2723,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -9610,10 +9610,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126544960</v>
+        <v>126532233</v>
       </c>
       <c r="B84" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9621,40 +9621,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>442834</v>
+        <v>442578</v>
       </c>
       <c r="R84" t="n">
-        <v>6733542</v>
+        <v>6733497</v>
       </c>
       <c r="S84" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9681,37 +9678,46 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126532233</v>
+        <v>126537460</v>
       </c>
       <c r="B85" t="n">
         <v>78980</v>
@@ -9746,10 +9752,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>442578</v>
+        <v>442496</v>
       </c>
       <c r="R85" t="n">
-        <v>6733497</v>
+        <v>6733706</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9781,7 +9787,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9791,7 +9797,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9818,10 +9824,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126537460</v>
+        <v>126544960</v>
       </c>
       <c r="B86" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9829,37 +9835,40 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>442496</v>
+        <v>442834</v>
       </c>
       <c r="R86" t="n">
-        <v>6733706</v>
+        <v>6733542</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9886,39 +9895,30 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 24131-2025 artfynd.xlsx
+++ b/artfynd/A 24131-2025 artfynd.xlsx
@@ -1981,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126532356</v>
+        <v>126534688</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,37 +1992,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442672</v>
+        <v>442816</v>
       </c>
       <c r="R14" t="n">
-        <v>6733497</v>
+        <v>6733589</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,12 +2076,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2302,45 +2302,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126534019</v>
+        <v>126535521</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442849</v>
+        <v>442661</v>
       </c>
       <c r="R17" t="n">
-        <v>6733592</v>
+        <v>6733562</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2377,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2382,7 +2387,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,7 +2414,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126533517</v>
+        <v>126534019</v>
       </c>
       <c r="B18" t="n">
         <v>78980</v>
@@ -2440,14 +2445,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442732</v>
+        <v>442849</v>
       </c>
       <c r="R18" t="n">
-        <v>6733607</v>
+        <v>6733592</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2484,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2489,7 +2494,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,50 +2521,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126535521</v>
+        <v>126533517</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442661</v>
+        <v>442732</v>
       </c>
       <c r="R19" t="n">
-        <v>6733562</v>
+        <v>6733607</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126534688</v>
+        <v>126532356</v>
       </c>
       <c r="B20" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,37 +2639,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442816</v>
+        <v>442672</v>
       </c>
       <c r="R20" t="n">
-        <v>6733589</v>
+        <v>6733497</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,12 +2723,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3371,10 +3371,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126536090</v>
+        <v>126545082</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3382,37 +3382,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442588</v>
+        <v>442504</v>
       </c>
       <c r="R27" t="n">
-        <v>6733620</v>
+        <v>6733693</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3439,46 +3442,37 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126534255</v>
+        <v>126536090</v>
       </c>
       <c r="B28" t="n">
         <v>78980</v>
@@ -3509,17 +3503,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>442816</v>
+        <v>442588</v>
       </c>
       <c r="R28" t="n">
-        <v>6733589</v>
+        <v>6733620</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3548,7 +3542,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3558,7 +3552,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3573,22 +3567,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126535579</v>
+        <v>126534255</v>
       </c>
       <c r="B29" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3596,21 +3590,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3655,7 +3649,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3665,7 +3659,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3685,60 +3679,55 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126536329</v>
+        <v>126535579</v>
       </c>
       <c r="B30" t="n">
-        <v>56849</v>
+        <v>78739</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442595</v>
+        <v>442816</v>
       </c>
       <c r="R30" t="n">
-        <v>6733618</v>
+        <v>6733589</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3767,7 +3756,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3777,12 +3766,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Balning</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3809,10 +3793,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126536898</v>
+        <v>126536329</v>
       </c>
       <c r="B31" t="n">
-        <v>98395</v>
+        <v>56849</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3820,37 +3804,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442534</v>
+        <v>442595</v>
       </c>
       <c r="R31" t="n">
-        <v>6733765</v>
+        <v>6733618</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3879,7 +3868,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3889,7 +3878,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Balning</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3904,44 +3898,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126536235</v>
+        <v>126536898</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>98395</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3951,10 +3945,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>442562</v>
+        <v>442534</v>
       </c>
       <c r="R32" t="n">
-        <v>6733675</v>
+        <v>6733765</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3986,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3996,7 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4023,10 +4017,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126545082</v>
+        <v>126536235</v>
       </c>
       <c r="B33" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4034,40 +4028,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>442504</v>
+        <v>442562</v>
       </c>
       <c r="R33" t="n">
-        <v>6733693</v>
+        <v>6733675</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4094,30 +4085,39 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -9610,10 +9610,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126532233</v>
+        <v>126544960</v>
       </c>
       <c r="B84" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9621,37 +9621,40 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>442578</v>
+        <v>442834</v>
       </c>
       <c r="R84" t="n">
-        <v>6733497</v>
+        <v>6733542</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9678,46 +9681,37 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126537460</v>
+        <v>126532233</v>
       </c>
       <c r="B85" t="n">
         <v>78980</v>
@@ -9752,10 +9746,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>442496</v>
+        <v>442578</v>
       </c>
       <c r="R85" t="n">
-        <v>6733706</v>
+        <v>6733497</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9787,7 +9781,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9797,7 +9791,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9824,10 +9818,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126544960</v>
+        <v>126537460</v>
       </c>
       <c r="B86" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9835,40 +9829,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>442834</v>
+        <v>442496</v>
       </c>
       <c r="R86" t="n">
-        <v>6733542</v>
+        <v>6733706</v>
       </c>
       <c r="S86" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9895,30 +9886,39 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10358,10 +10358,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126545041</v>
+        <v>126545058</v>
       </c>
       <c r="B91" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10369,21 +10369,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>442624</v>
+        <v>442626</v>
       </c>
       <c r="R91" t="n">
-        <v>6733705</v>
+        <v>6733676</v>
       </c>
       <c r="S91" t="n">
         <v>50</v>
@@ -10459,10 +10459,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126544939</v>
+        <v>126545041</v>
       </c>
       <c r="B92" t="n">
-        <v>91245</v>
+        <v>79598</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10470,21 +10470,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10497,10 +10497,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>442804</v>
+        <v>442624</v>
       </c>
       <c r="R92" t="n">
-        <v>6733651</v>
+        <v>6733705</v>
       </c>
       <c r="S92" t="n">
         <v>50</v>
@@ -10560,10 +10560,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126533418</v>
+        <v>126545073</v>
       </c>
       <c r="B93" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10571,37 +10571,40 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>442749</v>
+        <v>442502</v>
       </c>
       <c r="R93" t="n">
-        <v>6733551</v>
+        <v>6733702</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10628,49 +10631,40 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126533664</v>
+        <v>126544939</v>
       </c>
       <c r="B94" t="n">
-        <v>78739</v>
+        <v>91245</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10678,37 +10672,40 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>442805</v>
+        <v>442804</v>
       </c>
       <c r="R94" t="n">
-        <v>6733576</v>
+        <v>6733651</v>
       </c>
       <c r="S94" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10735,49 +10732,40 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126545058</v>
+        <v>126533418</v>
       </c>
       <c r="B95" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10785,40 +10773,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>442626</v>
+        <v>442749</v>
       </c>
       <c r="R95" t="n">
-        <v>6733676</v>
+        <v>6733551</v>
       </c>
       <c r="S95" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10845,37 +10830,46 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126545073</v>
+        <v>126533664</v>
       </c>
       <c r="B96" t="n">
         <v>78739</v>
@@ -10904,22 +10898,19 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>442502</v>
+        <v>442805</v>
       </c>
       <c r="R96" t="n">
-        <v>6733702</v>
+        <v>6733576</v>
       </c>
       <c r="S96" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10946,30 +10937,39 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>

--- a/artfynd/A 24131-2025 artfynd.xlsx
+++ b/artfynd/A 24131-2025 artfynd.xlsx
@@ -1342,7 +1342,7 @@
         <v>126533437</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126537010</v>
+        <v>126536839</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1457,21 +1457,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442497</v>
+        <v>442552</v>
       </c>
       <c r="R9" t="n">
-        <v>6733763</v>
+        <v>6733755</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126536839</v>
+        <v>126537010</v>
       </c>
       <c r="B10" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442552</v>
+        <v>442497</v>
       </c>
       <c r="R10" t="n">
-        <v>6733755</v>
+        <v>6733763</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,7 +1663,7 @@
         <v>126534875</v>
       </c>
       <c r="B11" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,17 +1760,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson, Karl Ericson, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126532558</v>
+        <v>126532413</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,17 +1798,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442670</v>
+        <v>442701</v>
       </c>
       <c r="R12" t="n">
-        <v>6733482</v>
+        <v>6733473</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,22 +1862,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126532413</v>
+        <v>126532558</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,17 +1905,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442701</v>
+        <v>442670</v>
       </c>
       <c r="R13" t="n">
-        <v>6733473</v>
+        <v>6733482</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,62 +1969,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126535521</v>
+        <v>126537449</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442661</v>
+        <v>442496</v>
       </c>
       <c r="R14" t="n">
-        <v>6733562</v>
+        <v>6733710</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,7 +2051,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2066,7 +2061,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,10 +2088,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126533517</v>
+        <v>126537753</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2128,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442732</v>
+        <v>442537</v>
       </c>
       <c r="R15" t="n">
-        <v>6733607</v>
+        <v>6733624</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,7 +2158,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2173,7 +2168,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2200,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126537753</v>
+        <v>126534688</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2211,37 +2206,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442537</v>
+        <v>442816</v>
       </c>
       <c r="R16" t="n">
-        <v>6733624</v>
+        <v>6733589</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2270,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2280,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,22 +2290,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126532356</v>
+        <v>126534019</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,14 +2333,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442672</v>
+        <v>442849</v>
       </c>
       <c r="R17" t="n">
-        <v>6733497</v>
+        <v>6733592</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,7 +2372,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2387,7 +2382,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126534019</v>
+        <v>126532356</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2445,14 +2440,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442849</v>
+        <v>442672</v>
       </c>
       <c r="R18" t="n">
-        <v>6733592</v>
+        <v>6733497</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,7 +2479,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2494,7 +2489,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2521,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126537449</v>
+        <v>126533517</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,10 +2551,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442496</v>
+        <v>442732</v>
       </c>
       <c r="R19" t="n">
-        <v>6733710</v>
+        <v>6733607</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,7 +2586,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2601,7 +2596,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,48 +2623,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126534688</v>
+        <v>126535521</v>
       </c>
       <c r="B20" t="n">
-        <v>78738</v>
+        <v>8447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442816</v>
+        <v>442661</v>
       </c>
       <c r="R20" t="n">
-        <v>6733589</v>
+        <v>6733562</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,22 +2723,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson, Karl Ericson, Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126537728</v>
+        <v>126534869</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2766,14 +2766,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442529</v>
+        <v>442797</v>
       </c>
       <c r="R21" t="n">
-        <v>6733634</v>
+        <v>6733657</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,7 +2845,7 @@
         <v>126533458</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2949,10 +2949,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126534869</v>
+        <v>126534242</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>442797</v>
+        <v>442855</v>
       </c>
       <c r="R23" t="n">
-        <v>6733657</v>
+        <v>6733530</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,7 +3059,7 @@
         <v>126532432</v>
       </c>
       <c r="B24" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3156,17 +3156,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Karl Ericson, Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126545006</v>
+        <v>126537728</v>
       </c>
       <c r="B25" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,40 +3174,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442689</v>
+        <v>442529</v>
       </c>
       <c r="R25" t="n">
-        <v>6733596</v>
+        <v>6733634</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3234,40 +3231,49 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126534242</v>
+        <v>126545006</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,37 +3281,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442855</v>
+        <v>442689</v>
       </c>
       <c r="R26" t="n">
-        <v>6733530</v>
+        <v>6733596</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3332,87 +3341,83 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126534892</v>
+        <v>126536329</v>
       </c>
       <c r="B27" t="n">
-        <v>78739</v>
+        <v>56849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442816</v>
+        <v>442595</v>
       </c>
       <c r="R27" t="n">
-        <v>6733589</v>
+        <v>6733618</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3441,7 +3446,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3451,7 +3456,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Balning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3471,7 +3481,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson, Karl Ericson, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3481,7 +3491,7 @@
         <v>126536898</v>
       </c>
       <c r="B28" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3585,10 +3595,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126536235</v>
+        <v>126534892</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3596,37 +3606,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>442562</v>
+        <v>442816</v>
       </c>
       <c r="R29" t="n">
-        <v>6733675</v>
+        <v>6733589</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3655,7 +3665,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3665,7 +3675,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3680,22 +3690,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126536090</v>
+        <v>126545082</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3703,37 +3713,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442588</v>
+        <v>442504</v>
       </c>
       <c r="R30" t="n">
-        <v>6733620</v>
+        <v>6733693</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3760,49 +3773,40 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126545082</v>
+        <v>126534255</v>
       </c>
       <c r="B31" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3810,40 +3814,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442504</v>
+        <v>442816</v>
       </c>
       <c r="R31" t="n">
-        <v>6733693</v>
+        <v>6733589</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3870,83 +3871,87 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126536329</v>
+        <v>126536235</v>
       </c>
       <c r="B32" t="n">
-        <v>56849</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>442595</v>
+        <v>442562</v>
       </c>
       <c r="R32" t="n">
-        <v>6733618</v>
+        <v>6733675</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3975,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3985,12 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Balning</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4005,22 +4005,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson, Karl Ericson, Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126534255</v>
+        <v>126536090</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,17 +4048,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>442816</v>
+        <v>442588</v>
       </c>
       <c r="R33" t="n">
-        <v>6733589</v>
+        <v>6733620</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4112,71 +4112,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126536298</v>
+        <v>126537716</v>
       </c>
       <c r="B34" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>442553</v>
+        <v>442527</v>
       </c>
       <c r="R34" t="n">
-        <v>6733706</v>
+        <v>6733645</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4208,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4218,12 +4204,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>5 bladrosetter.</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4250,10 +4231,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126536210</v>
+        <v>126536609</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4285,10 +4266,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>442563</v>
+        <v>442496</v>
       </c>
       <c r="R35" t="n">
-        <v>6733672</v>
+        <v>6733746</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4320,7 +4301,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4330,7 +4311,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,10 +4338,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126537716</v>
+        <v>126536210</v>
       </c>
       <c r="B36" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4392,10 +4373,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>442527</v>
+        <v>442563</v>
       </c>
       <c r="R36" t="n">
-        <v>6733645</v>
+        <v>6733672</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4427,7 +4408,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4437,7 +4418,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4464,45 +4445,59 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126536828</v>
+        <v>126536298</v>
       </c>
       <c r="B37" t="n">
-        <v>78739</v>
+        <v>98436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>442554</v>
+        <v>442553</v>
       </c>
       <c r="R37" t="n">
-        <v>6733752</v>
+        <v>6733706</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4534,7 +4529,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4544,7 +4539,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>5 bladrosetter.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4571,10 +4571,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126536609</v>
+        <v>126536828</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4582,21 +4582,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442496</v>
+        <v>442554</v>
       </c>
       <c r="R38" t="n">
-        <v>6733746</v>
+        <v>6733752</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4678,45 +4678,59 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126534895</v>
+        <v>126536368</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442795</v>
+        <v>442550</v>
       </c>
       <c r="R39" t="n">
-        <v>6733678</v>
+        <v>6733706</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4748,7 +4762,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4758,7 +4772,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4785,62 +4799,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126536368</v>
+        <v>126536943</v>
       </c>
       <c r="B40" t="n">
-        <v>98361</v>
+        <v>80143</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442550</v>
+        <v>442595</v>
       </c>
       <c r="R40" t="n">
-        <v>6733706</v>
+        <v>6733618</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4894,12 +4894,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4909,7 +4909,7 @@
         <v>126536540</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,48 +5013,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126536943</v>
+        <v>126534895</v>
       </c>
       <c r="B42" t="n">
-        <v>80112</v>
+        <v>79011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>442595</v>
+        <v>442795</v>
       </c>
       <c r="R42" t="n">
-        <v>6733618</v>
+        <v>6733678</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5108,12 +5108,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karl Ericson, Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
         <v>126532164</v>
       </c>
       <c r="B43" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5217,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126535429</v>
+        <v>126536000</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>442676</v>
+        <v>442621</v>
       </c>
       <c r="R44" t="n">
-        <v>6733613</v>
+        <v>6733565</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5297,12 +5297,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5329,59 +5324,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126536262</v>
+        <v>126535429</v>
       </c>
       <c r="B45" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>442558</v>
+        <v>442676</v>
       </c>
       <c r="R45" t="n">
-        <v>6733690</v>
+        <v>6733613</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,7 +5394,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5423,7 +5404,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5450,48 +5436,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126535340</v>
+        <v>126534016</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>80018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442705</v>
+        <v>442816</v>
       </c>
       <c r="R46" t="n">
-        <v>6733607</v>
+        <v>6733589</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5520,7 +5506,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5530,7 +5516,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5545,22 +5531,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126536000</v>
+        <v>126535381</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5592,10 +5578,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>442621</v>
+        <v>442681</v>
       </c>
       <c r="R47" t="n">
-        <v>6733565</v>
+        <v>6733614</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5627,7 +5613,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5637,7 +5623,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5664,48 +5650,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126534016</v>
+        <v>126535340</v>
       </c>
       <c r="B48" t="n">
-        <v>79987</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>442816</v>
+        <v>442705</v>
       </c>
       <c r="R48" t="n">
-        <v>6733589</v>
+        <v>6733607</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5734,7 +5720,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5744,7 +5730,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5759,57 +5745,71 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson, Karl Ericson, Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126535381</v>
+        <v>126536262</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>442681</v>
+        <v>442558</v>
       </c>
       <c r="R49" t="n">
-        <v>6733614</v>
+        <v>6733690</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5881,7 +5881,7 @@
         <v>126534774</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5985,57 +5985,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126536612</v>
+        <v>126532174</v>
       </c>
       <c r="B51" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442595</v>
+        <v>442587</v>
       </c>
       <c r="R51" t="n">
-        <v>6733618</v>
+        <v>6733482</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6064,7 +6055,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6074,7 +6065,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6089,22 +6080,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126533900</v>
+        <v>126534694</v>
       </c>
       <c r="B52" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6112,21 +6103,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6136,10 +6127,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442790</v>
+        <v>442844</v>
       </c>
       <c r="R52" t="n">
-        <v>6733600</v>
+        <v>6733536</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6171,7 +6162,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6181,7 +6172,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6208,48 +6199,57 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126534694</v>
+        <v>126536612</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442844</v>
+        <v>442595</v>
       </c>
       <c r="R53" t="n">
-        <v>6733536</v>
+        <v>6733618</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6303,22 +6303,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126532174</v>
+        <v>126533900</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6326,34 +6326,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442587</v>
+        <v>442790</v>
       </c>
       <c r="R54" t="n">
-        <v>6733482</v>
+        <v>6733600</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6422,10 +6422,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126533506</v>
+        <v>126534926</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>442734</v>
+        <v>442793</v>
       </c>
       <c r="R55" t="n">
-        <v>6733610</v>
+        <v>6733682</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6529,10 +6529,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126533495</v>
+        <v>126533506</v>
       </c>
       <c r="B56" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442742</v>
+        <v>442734</v>
       </c>
       <c r="R56" t="n">
-        <v>6733609</v>
+        <v>6733610</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6636,10 +6636,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126534926</v>
+        <v>126532998</v>
       </c>
       <c r="B57" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6667,14 +6667,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442793</v>
+        <v>442725</v>
       </c>
       <c r="R57" t="n">
-        <v>6733682</v>
+        <v>6733534</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6743,10 +6743,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126533259</v>
+        <v>126533495</v>
       </c>
       <c r="B58" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6754,21 +6754,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442752</v>
+        <v>442742</v>
       </c>
       <c r="R58" t="n">
-        <v>6733552</v>
+        <v>6733609</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6850,48 +6850,62 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126536931</v>
+        <v>126534189</v>
       </c>
       <c r="B59" t="n">
-        <v>80043</v>
+        <v>98436</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442595</v>
+        <v>442855</v>
       </c>
       <c r="R59" t="n">
-        <v>6733618</v>
+        <v>6733559</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6920,7 +6934,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6930,7 +6944,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Bladrosetter över ca 1kv/m. 30+</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6945,74 +6964,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Karl Ericson, Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126534189</v>
+        <v>126536931</v>
       </c>
       <c r="B60" t="n">
-        <v>98361</v>
+        <v>80074</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442855</v>
+        <v>442595</v>
       </c>
       <c r="R60" t="n">
-        <v>6733559</v>
+        <v>6733618</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7041,7 +7046,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7051,12 +7056,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Bladrosetter över ca 1kv/m. 30+</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7071,22 +7071,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126532998</v>
+        <v>126533259</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7094,34 +7094,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442725</v>
+        <v>442752</v>
       </c>
       <c r="R61" t="n">
-        <v>6733534</v>
+        <v>6733552</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7190,53 +7190,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126534107</v>
+        <v>126533468</v>
       </c>
       <c r="B62" t="n">
-        <v>56849</v>
+        <v>79011</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442816</v>
+        <v>442751</v>
       </c>
       <c r="R62" t="n">
-        <v>6733589</v>
+        <v>6733598</v>
       </c>
       <c r="S62" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7265,7 +7260,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7275,7 +7270,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7290,12 +7285,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson, Karl Ericson, Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7305,7 +7300,7 @@
         <v>126533981</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7412,7 +7407,7 @@
         <v>126533027</v>
       </c>
       <c r="B64" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7516,48 +7511,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126533468</v>
+        <v>126534107</v>
       </c>
       <c r="B65" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442751</v>
+        <v>442816</v>
       </c>
       <c r="R65" t="n">
-        <v>6733598</v>
+        <v>6733589</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7611,12 +7611,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7626,7 +7626,7 @@
         <v>126536549</v>
       </c>
       <c r="B66" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7730,57 +7730,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126536970</v>
+        <v>126534912</v>
       </c>
       <c r="B67" t="n">
-        <v>98395</v>
+        <v>79011</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>442595</v>
+        <v>442796</v>
       </c>
       <c r="R67" t="n">
-        <v>6733618</v>
+        <v>6733680</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7809,7 +7800,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7819,7 +7810,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7834,22 +7825,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Karl Ericson, Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126534912</v>
+        <v>126534831</v>
       </c>
       <c r="B68" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7881,10 +7872,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>442796</v>
+        <v>442826</v>
       </c>
       <c r="R68" t="n">
-        <v>6733680</v>
+        <v>6733603</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7916,7 +7907,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7926,7 +7917,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7953,10 +7944,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126535244</v>
+        <v>126532344</v>
       </c>
       <c r="B69" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7988,10 +7979,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>442724</v>
+        <v>442669</v>
       </c>
       <c r="R69" t="n">
-        <v>6733608</v>
+        <v>6733498</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8023,7 +8014,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8033,7 +8024,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8060,10 +8051,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126534831</v>
+        <v>126535244</v>
       </c>
       <c r="B70" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8091,14 +8082,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>442826</v>
+        <v>442724</v>
       </c>
       <c r="R70" t="n">
-        <v>6733603</v>
+        <v>6733608</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8130,7 +8121,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8140,7 +8131,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8167,48 +8158,57 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126532344</v>
+        <v>126536970</v>
       </c>
       <c r="B71" t="n">
-        <v>78980</v>
+        <v>98470</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>442669</v>
+        <v>442595</v>
       </c>
       <c r="R71" t="n">
-        <v>6733498</v>
+        <v>6733618</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8262,22 +8262,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126535271</v>
+        <v>126536095</v>
       </c>
       <c r="B72" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8285,37 +8285,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>442720</v>
+        <v>442816</v>
       </c>
       <c r="R72" t="n">
-        <v>6733609</v>
+        <v>6733589</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8344,7 +8349,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8354,7 +8359,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8369,60 +8374,74 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126536348</v>
+        <v>126537111</v>
       </c>
       <c r="B73" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>442595</v>
+        <v>442479</v>
       </c>
       <c r="R73" t="n">
-        <v>6733618</v>
+        <v>6733796</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8451,7 +8470,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8461,7 +8480,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8476,71 +8495,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson, Karl Ericson, Lars-Erik Nilsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126537111</v>
+        <v>126535271</v>
       </c>
       <c r="B74" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>442479</v>
+        <v>442720</v>
       </c>
       <c r="R74" t="n">
-        <v>6733796</v>
+        <v>6733609</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8572,7 +8577,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8582,7 +8587,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8612,7 +8617,7 @@
         <v>126533971</v>
       </c>
       <c r="B75" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8716,10 +8721,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126536095</v>
+        <v>126536348</v>
       </c>
       <c r="B76" t="n">
-        <v>57817</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8727,42 +8732,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>442816</v>
+        <v>442595</v>
       </c>
       <c r="R76" t="n">
-        <v>6733589</v>
+        <v>6733618</v>
       </c>
       <c r="S76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson, Karl Ericson, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8831,7 +8831,7 @@
         <v>126533520</v>
       </c>
       <c r="B77" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8935,59 +8935,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126536383</v>
+        <v>126533153</v>
       </c>
       <c r="B78" t="n">
-        <v>98361</v>
+        <v>56849</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>442548</v>
+        <v>442518</v>
       </c>
       <c r="R78" t="n">
-        <v>6733706</v>
+        <v>6733634</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9019,7 +9005,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9029,7 +9015,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Spillning, äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9044,57 +9035,71 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126533153</v>
+        <v>126536383</v>
       </c>
       <c r="B79" t="n">
-        <v>56849</v>
+        <v>98436</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>442518</v>
+        <v>442548</v>
       </c>
       <c r="R79" t="n">
-        <v>6733634</v>
+        <v>6733706</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9126,7 +9131,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9136,12 +9141,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Spillning, äldre</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9156,12 +9156,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9171,7 +9171,7 @@
         <v>126536344</v>
       </c>
       <c r="B80" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>126533758</v>
       </c>
       <c r="B81" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9396,10 +9396,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126533508</v>
+        <v>126534807</v>
       </c>
       <c r="B82" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9431,10 +9431,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>442733</v>
+        <v>442826</v>
       </c>
       <c r="R82" t="n">
-        <v>6733609</v>
+        <v>6733598</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9503,10 +9503,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126534807</v>
+        <v>126533508</v>
       </c>
       <c r="B83" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9538,10 +9538,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>442826</v>
+        <v>442733</v>
       </c>
       <c r="R83" t="n">
-        <v>6733598</v>
+        <v>6733609</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9610,10 +9610,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126544960</v>
+        <v>126532233</v>
       </c>
       <c r="B84" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9621,40 +9621,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>442834</v>
+        <v>442578</v>
       </c>
       <c r="R84" t="n">
-        <v>6733542</v>
+        <v>6733497</v>
       </c>
       <c r="S84" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9681,40 +9678,49 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126532233</v>
+        <v>126537460</v>
       </c>
       <c r="B85" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9746,10 +9752,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>442578</v>
+        <v>442496</v>
       </c>
       <c r="R85" t="n">
-        <v>6733497</v>
+        <v>6733706</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9781,7 +9787,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9791,7 +9797,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9818,10 +9824,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126537460</v>
+        <v>126544960</v>
       </c>
       <c r="B86" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9829,37 +9835,40 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>442496</v>
+        <v>442834</v>
       </c>
       <c r="R86" t="n">
-        <v>6733706</v>
+        <v>6733542</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9886,49 +9895,40 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126534663</v>
+        <v>126544939</v>
       </c>
       <c r="B87" t="n">
-        <v>79598</v>
+        <v>91319</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9936,37 +9936,40 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>442855</v>
+        <v>442804</v>
       </c>
       <c r="R87" t="n">
-        <v>6733544</v>
+        <v>6733651</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9993,49 +9996,40 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126544939</v>
+        <v>126545058</v>
       </c>
       <c r="B88" t="n">
-        <v>91245</v>
+        <v>78770</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10043,21 +10037,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10070,10 +10064,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>442804</v>
+        <v>442626</v>
       </c>
       <c r="R88" t="n">
-        <v>6733651</v>
+        <v>6733676</v>
       </c>
       <c r="S88" t="n">
         <v>50</v>
@@ -10133,10 +10127,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126533664</v>
+        <v>126545073</v>
       </c>
       <c r="B89" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10162,19 +10156,22 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Bötå böj, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>442805</v>
+        <v>442502</v>
       </c>
       <c r="R89" t="n">
-        <v>6733576</v>
+        <v>6733702</v>
       </c>
       <c r="S89" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10201,49 +10198,40 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126532363</v>
+        <v>126533664</v>
       </c>
       <c r="B90" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10251,37 +10239,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Bötå böj, Bötå böj, Dlr</t>
+          <t>Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>442675</v>
+        <v>442805</v>
       </c>
       <c r="R90" t="n">
-        <v>6733482</v>
+        <v>6733576</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10310,7 +10298,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10320,7 +10308,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10335,12 +10323,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10350,7 +10338,7 @@
         <v>126532387</v>
       </c>
       <c r="B91" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10454,10 +10442,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126533418</v>
+        <v>126545041</v>
       </c>
       <c r="B92" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10465,37 +10453,40 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
+          <t>Bötå Böj, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>442749</v>
+        <v>442624</v>
       </c>
       <c r="R92" t="n">
-        <v>6733551</v>
+        <v>6733705</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10522,49 +10513,40 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126545073</v>
+        <v>126534663</v>
       </c>
       <c r="B93" t="n">
-        <v>78739</v>
+        <v>79629</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10572,40 +10554,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>442502</v>
+        <v>442855</v>
       </c>
       <c r="R93" t="n">
-        <v>6733702</v>
+        <v>6733544</v>
       </c>
       <c r="S93" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10632,40 +10611,49 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126545041</v>
+        <v>126533418</v>
       </c>
       <c r="B94" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10673,40 +10661,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Kättbo besparingsskog, Kättbo besparingsskog, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>442624</v>
+        <v>442749</v>
       </c>
       <c r="R94" t="n">
-        <v>6733705</v>
+        <v>6733551</v>
       </c>
       <c r="S94" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10733,80 +10718,84 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126533010</v>
+        <v>126532363</v>
       </c>
       <c r="B95" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>442722</v>
+        <v>442675</v>
       </c>
       <c r="R95" t="n">
-        <v>6733535</v>
+        <v>6733482</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10838,7 +10827,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10848,7 +10837,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10875,51 +10864,53 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126545058</v>
+        <v>126533010</v>
       </c>
       <c r="B96" t="n">
-        <v>78739</v>
+        <v>8447</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bötå Böj, Dlr</t>
+          <t>Bötå böj, Bötå böj, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>442626</v>
+        <v>442722</v>
       </c>
       <c r="R96" t="n">
-        <v>6733676</v>
+        <v>6733535</v>
       </c>
       <c r="S96" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10946,62 +10937,71 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126533580</v>
+        <v>126534551</v>
       </c>
       <c r="B97" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11011,10 +11011,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>442805</v>
+        <v>442861</v>
       </c>
       <c r="R97" t="n">
-        <v>6733603</v>
+        <v>6733550</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11083,32 +11083,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126534551</v>
+        <v>126533580</v>
       </c>
       <c r="B98" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11118,10 +11118,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>442861</v>
+        <v>442805</v>
       </c>
       <c r="R98" t="n">
-        <v>6733550</v>
+        <v>6733603</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11153,7 +11153,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11193,7 +11193,7 @@
         <v>126533405</v>
       </c>
       <c r="B99" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson, Karl Ericson, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -11309,7 +11309,7 @@
         <v>126537899</v>
       </c>
       <c r="B100" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Karl Ericson, Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson, Karl Ericson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
